--- a/Data_clean/MCAS/Estados_US/Edos_USA_2018/VERMONT_2018.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2018/VERMONT_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Las Rosas</t>
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -460,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -617,7 +672,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C18">
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>San Francisco Logueche</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>San Jerónimo Coatlán</t>
@@ -667,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>San Pedro y San Pablo Teposcolula</t>
+          <t>San Pedro Y San Pablo Teposcolula</t>
         </is>
       </c>
       <c r="C22">
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Santa María Ipalapa</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -706,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Villa de Etla</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C25">
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Tecomatlán</t>
@@ -776,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tepatlaxco de Hidalgo</t>
+          <t>Tepatlaxco De Hidalgo</t>
         </is>
       </c>
       <c r="C30">
@@ -789,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -895,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -908,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -921,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -952,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -965,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -978,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C44">
@@ -991,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C45">
@@ -1004,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Tlacotalpan</t>
@@ -1017,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -1030,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1053,41 +1233,6 @@
       </c>
       <c r="D49">
         <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
